--- a/data/trans_orig/IP39B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Estudios-trans_orig.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>30897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>54143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60977</t>
+          <t>60986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41753</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40040</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54386</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77604</t>
+          <t>77556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162290</t>
+          <t>162222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181265</t>
+          <t>180446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193123</t>
+          <t>192452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211905</t>
+          <t>211381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361507</t>
+          <t>360558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387720</t>
+          <t>386622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55552</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>81331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96598</t>
+          <t>98502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75929</t>
+          <t>76355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91063</t>
+          <t>91243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>162719</t>
+          <t>162436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>184856</t>
+          <t>184703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>278170</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>303646</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>588313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>624468</t>
+          <t>623294</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46136</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>28768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>49071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157166</t>
+          <t>156155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171460</t>
+          <t>171222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163647</t>
+          <t>162695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180486</t>
+          <t>179926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324975</t>
+          <t>325228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348367</t>
+          <t>347267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63500</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>79419</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75710</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90022</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144548</t>
+          <t>144199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165805</t>
+          <t>165176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28138</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>249229</t>
+          <t>248741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271182</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>284226</t>
+          <t>285319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>517267</t>
+          <t>518936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>551568</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45828</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178811</t>
+          <t>179120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193813</t>
+          <t>193257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192843</t>
+          <t>192062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208294</t>
+          <t>207348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377432</t>
+          <t>376970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399277</t>
+          <t>398048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25958</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79289</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93868</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93395</t>
+          <t>93348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108325</t>
+          <t>108053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178495</t>
+          <t>178032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199431</t>
+          <t>197417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57332</t>
+          <t>58119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276656</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>588387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>620637</t>
+          <t>620559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP39B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3787</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4339</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3096</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4668</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1174,74 +1174,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25282</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>29417</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26637</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26065</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>30797</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28883</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>25381</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>30897</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>54014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60986</t>
+          <t>60982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30797</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30797</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30797</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5579</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7597</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4038</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8670</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1635,67 +1635,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>3595</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7382</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7830</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3951</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7760</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31384</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23528</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40177</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33109</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25546</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25125</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42482</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>31384</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23638</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40453</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53625</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77556</t>
+          <t>77476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202484</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192355</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>211694</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>172291</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162222</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180446</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>161550</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>180943</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202484</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192452</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>211381</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360558</t>
+          <t>360563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386622</t>
+          <t>386276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>243713</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>243713</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>243713</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>213243</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>213243</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>213243</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>243713</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>243713</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>243713</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,67 +2091,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4855</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2134</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5330</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5789</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5461</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6494</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>3603</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8074</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8346</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2647</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6150</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>4347</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9054</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8945</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7624</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21394</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15073</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29138</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>24107</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>16690</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>31373</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>17245</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>32179</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>19,4%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>14831</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>28462</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>55695</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>84066</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>75675</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>91308</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>80,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>90052</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>81331</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>98502</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>81402</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>98157</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>72,48%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>84066</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>76355</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>91243</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>162436</t>
+          <t>162504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>184703</t>
+          <t>184739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>113855</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>113855</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>113855</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>124243</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>124243</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>124243</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>113855</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>113855</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>113855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3886</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2755</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6420</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7933</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2886,67 +2886,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>6686</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11664</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>7230</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>3556</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>12909</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>13214</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3907</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>12715</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9039</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>14324</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>8676</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13791</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14348</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9039</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>14965</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>54714</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>45213</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>66099</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>57863</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>47013</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>70260</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>46813</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>69791</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>15,71%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>54714</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>44917</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>66526</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97791</t>
+          <t>96909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129354</t>
+          <t>126977</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>315431</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>302085</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>326053</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>80,93%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>437</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>291760</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>278170</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>304111</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>278457</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>304261</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>79,22%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>315431</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>302472</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>327219</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>80,93%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588313</t>
+          <t>590631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>623294</t>
+          <t>624733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>389756</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>389756</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>389756</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>551</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>368283</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>368283</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>368283</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>389756</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>389756</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>389756</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,107 +3681,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2676</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -4025,67 +4025,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2436</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1955</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -4133,72 +4133,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18984</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24110</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20672</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26063</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20475</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25903</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18984</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14791</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>20771</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21420</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21420</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21420</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>26660</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>26660</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>26660</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21420</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21420</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5606</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5605</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1395</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4352</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7496</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12655</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2920</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6105</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6817</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7496</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3612</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21088</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14977</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29016</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18104</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12305</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12492</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25542</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21088</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15065</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30115</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172099</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180020</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>164879</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156155</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171222</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156436</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>171036</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172099</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162695</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>179926</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>325228</t>
+          <t>324397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347267</t>
+          <t>347508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204812</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204812</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204812</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187926</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187926</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187926</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204812</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204812</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8370</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2755</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8048</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6272</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7985</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6435</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7193</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3789</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12517</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12659</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -5384,72 +5384,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16755</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11029</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23066</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>20139</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13848</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>27477</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>27250</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>16755</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>10732</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>23595</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -5497,72 +5497,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>82956</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>74644</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>89842</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>76,56%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>82,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>71973</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>64017</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>79419</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>64077</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>78946</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>70,07%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>82956</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>74699</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>89719</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>76,56%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144199</t>
+          <t>143243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165176</t>
+          <t>165425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>108359</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>108359</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>108359</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>102716</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>102716</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>102716</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>108359</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>108359</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>108359</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11444</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>3977</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8185</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11131</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5164</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9812</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>2051</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>5164</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>10116</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9402</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15340</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>10114</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6049</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>15936</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>5964</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>16127</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9402</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5313</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>40279</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>31462</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>50334</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>40198</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>31011</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>50300</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>31581</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>50348</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>12,67%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>40279</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>31168</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>50792</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67471</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95253</t>
+          <t>94717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>274039</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>262183</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>285498</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>81,9%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>78,36%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>260962</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>248741</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>271594</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>250550</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>271984</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>82,24%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>78,39%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>85,59%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>274039</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>262097</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>285319</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>81,9%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>518936</t>
+          <t>517742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>551817</t>
+          <t>550926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>334591</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>334591</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>334591</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>317302</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>317302</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>317302</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>334591</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>334591</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>334591</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6753,107 +6753,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>540</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -6866,107 +6866,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3052</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -6979,107 +6979,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3694</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1192</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3860</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3764</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -7092,74 +7092,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18271</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15769</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11700</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9247</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>12804</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>73,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18271</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15603</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19463</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>42</t>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31695</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>12804</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>12804</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>12804</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19463</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19463</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19463</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7327,102 +7327,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3640</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4210</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3786</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3401</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6741</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11488</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2758</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6750</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6741</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12786</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17407</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11418</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24716</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18639</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13436</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25755</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12665</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25798</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17407</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11794</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24898</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46681</t>
+          <t>46013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>200913</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192382</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207993</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>187219</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179120</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>193257</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>179325</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>193843</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>200913</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192062</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207348</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376970</t>
+          <t>376118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398048</t>
+          <t>398126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210090</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210090</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210090</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226738</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226738</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8409</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2072</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1469</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8450</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -8122,67 +8122,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7559</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>2458</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5858</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7054</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3066</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7393</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4680</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9560</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -8343,72 +8343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19080</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>18861</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13716</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>25780</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>26227</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>16,59%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>12834</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>7941</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>19339</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -8456,72 +8456,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>101221</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>94023</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>108686</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>87241</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>79550</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>93548</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>79387</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>93763</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>76,73%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>69,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>82,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>101221</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>93348</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>108053</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178032</t>
+          <t>176292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>197417</t>
+          <t>198151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>125965</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>125965</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>125965</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>113697</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>113697</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>113697</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>125965</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>125965</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>125965</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9537</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2793</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>723</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7013</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -8804,67 +8804,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9183</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>3750</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7570</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7908</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4151</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>8220</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8912,107 +8912,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11422</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6592</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>17832</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>6388</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12405</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>17810</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>6582</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>17840</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>17810</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>12055</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>25440</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>31433</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>23993</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>41220</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>37500</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>28776</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>46838</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>29438</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>47220</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>31433</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>23535</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>40474</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58119</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84493</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>320405</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>308699</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>329933</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>82,95%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>286160</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>274531</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>295688</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>275779</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>295822</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>85,02%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>81,56%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>320405</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>308410</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>331188</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,09%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588387</t>
+          <t>590309</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>620559</t>
+          <t>620306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>372166</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>372166</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>372166</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>336591</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>336591</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>336591</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>372166</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>372166</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>372166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
